--- a/projects/EMG-BioInputs/EMG-BioInputs-BOM.xlsx
+++ b/projects/EMG-BioInputs/EMG-BioInputs-BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SorokinVlady\Documents\Arduino\projects\EMG PC Controls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SorokinVlady\Documents\Arduino\projects\EMG-BioInputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12ACF86-505F-4FBD-898C-65C3ADE1402B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B99B3B-BB2E-436F-B2A8-139B87D4EB20}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3765" yWindow="3765" windowWidth="28800" windowHeight="15345" xr2:uid="{07024F4D-E5C7-4B8A-AB6A-143DE046C366}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>https://www.digikey.at/de/products/detail/sparkfun-electronics/12970/6833933</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Link</t>
   </si>
   <si>
-    <t>гелевые пады</t>
-  </si>
-  <si>
     <t>35RASMT2BHNTRX</t>
   </si>
   <si>
@@ -88,6 +85,33 @@
   </si>
   <si>
     <t>Notes:</t>
+  </si>
+  <si>
+    <t>https://www.kardiodepot.at/s/46503_319169_-3m-red-dot-2660-5-holter-elektroden-rontgentransluzent</t>
+  </si>
+  <si>
+    <t>3M Red Dot 2660-5</t>
+  </si>
+  <si>
+    <t>Electrodes Type 1</t>
+  </si>
+  <si>
+    <t>3M Red Dot 2560</t>
+  </si>
+  <si>
+    <t>Electrodes Type 2</t>
+  </si>
+  <si>
+    <t>https://www.kardiodepot.at/s/46503_319164_-3m-red-dot-2560-holter-elektroden</t>
+  </si>
+  <si>
+    <t>https://www.kardiodepot.at/s/46588_367004_clinical-l55h-elektroden-fur-holter</t>
+  </si>
+  <si>
+    <t>Clinical L55H-Elektroden</t>
+  </si>
+  <si>
+    <t>Electrodes Type 3</t>
   </si>
 </sst>
 </file>
@@ -593,7 +617,7 @@
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="48.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
     <col min="5" max="7" width="11.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="74.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.85546875" style="1" customWidth="1"/>
@@ -605,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>2</v>
@@ -620,15 +644,15 @@
         <v>5</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="3:10" ht="15" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -646,81 +670,133 @@
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" ref="G5:G10" si="0">F5*E5</f>
+        <v>12.825000000000001</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" ref="G5:G7" si="0">F5*E5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>0.51300000000000001</v>
+        <v>1.5164</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="0"/>
-        <v>12.825000000000001</v>
+        <v>37.909999999999997</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="C7" s="3"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>25.2</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="2">
-        <v>1.5164</v>
-      </c>
-      <c r="G7" s="2">
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G10" s="2">
         <f t="shared" si="0"/>
-        <v>37.909999999999997</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="H10" s="5"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F11" s="2"/>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="F12" s="2"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -735,7 +811,7 @@
     <row r="14" spans="3:10" ht="15" thickTop="1" x14ac:dyDescent="0.2">
       <c r="G14" s="2">
         <f>SUM(G4:G13)</f>
-        <v>152.01499999999999</v>
+        <v>234.81499999999997</v>
       </c>
       <c r="H14" s="5"/>
     </row>

--- a/projects/EMG-BioInputs/EMG-BioInputs-BOM.xlsx
+++ b/projects/EMG-BioInputs/EMG-BioInputs-BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SorokinVlady\Documents\Arduino\projects\EMG-BioInputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SorokinVlady\Documents\Arduino\projects\EMG PC Controls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B99B3B-BB2E-436F-B2A8-139B87D4EB20}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12ACF86-505F-4FBD-898C-65C3ADE1402B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3765" yWindow="3765" windowWidth="28800" windowHeight="15345" xr2:uid="{07024F4D-E5C7-4B8A-AB6A-143DE046C366}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>https://www.digikey.at/de/products/detail/sparkfun-electronics/12970/6833933</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Link</t>
   </si>
   <si>
+    <t>гелевые пады</t>
+  </si>
+  <si>
     <t>35RASMT2BHNTRX</t>
   </si>
   <si>
@@ -85,33 +88,6 @@
   </si>
   <si>
     <t>Notes:</t>
-  </si>
-  <si>
-    <t>https://www.kardiodepot.at/s/46503_319169_-3m-red-dot-2660-5-holter-elektroden-rontgentransluzent</t>
-  </si>
-  <si>
-    <t>3M Red Dot 2660-5</t>
-  </si>
-  <si>
-    <t>Electrodes Type 1</t>
-  </si>
-  <si>
-    <t>3M Red Dot 2560</t>
-  </si>
-  <si>
-    <t>Electrodes Type 2</t>
-  </si>
-  <si>
-    <t>https://www.kardiodepot.at/s/46503_319164_-3m-red-dot-2560-holter-elektroden</t>
-  </si>
-  <si>
-    <t>https://www.kardiodepot.at/s/46588_367004_clinical-l55h-elektroden-fur-holter</t>
-  </si>
-  <si>
-    <t>Clinical L55H-Elektroden</t>
-  </si>
-  <si>
-    <t>Electrodes Type 3</t>
   </si>
 </sst>
 </file>
@@ -617,7 +593,7 @@
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="48.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="1" customWidth="1"/>
     <col min="5" max="7" width="11.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="74.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.85546875" style="1" customWidth="1"/>
@@ -629,7 +605,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>2</v>
@@ -644,15 +620,15 @@
         <v>5</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="3:10" ht="15" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -670,133 +646,81 @@
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" ref="G5:G7" si="0">F5*E5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1">
-        <v>25</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.51300000000000001</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" ref="G5:G10" si="0">F5*E5</f>
-        <v>12.825000000000001</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>1.5164</v>
+        <v>0.51300000000000001</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="0"/>
-        <v>37.909999999999997</v>
+        <v>12.825000000000001</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C7" s="3"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="5"/>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.5164</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="0"/>
+        <v>37.909999999999997</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>39.200000000000003</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="2">
-        <v>12.6</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="0"/>
-        <v>25.2</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="F11" s="2"/>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.2">
-      <c r="F12" s="2"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -811,7 +735,7 @@
     <row r="14" spans="3:10" ht="15" thickTop="1" x14ac:dyDescent="0.2">
       <c r="G14" s="2">
         <f>SUM(G4:G13)</f>
-        <v>234.81499999999997</v>
+        <v>152.01499999999999</v>
       </c>
       <c r="H14" s="5"/>
     </row>
